--- a/kioxia/dist/20261025_Kioxia模型_v0.1.xlsx
+++ b/kioxia/dist/20261025_Kioxia模型_v0.1.xlsx
@@ -9578,7 +9578,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -21460,7 +21460,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -22317,7 +22317,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -27499,7 +27499,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.xlsx</t>
+      <t xml:space="preserve">_v0.4.1.xlsx</t>
     </r>
   </si>
   <si>
